--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_loadingtips/lang_loadingtips__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_loadingtips/lang_loadingtips__lore__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Skills mạnh được thực hiện bởi 2 Resonators. Khi Concerto Vibrancy được nạp đầy, việc chuyển đổi Resonators sẽ tiêu hao toàn bộ và kích hoạt Concerto Effect dựa trên thuộc tính tấn công của nhân vật được chuyển đổi.</t>
+          <t>Kỹ năng mạnh được thực hiện bởi 2 Resonator. Khi Năng Lượng Giao Hưởng được nạp đầy, chuyển đổi Resonator sẽ tiêu hao toàn bộ và kích hoạt Hiệu Ứng Giao Hưởng dựa trên thuộc tính tấn công của nhân vật được chuyển đến.</t>
         </is>
       </c>
     </row>
